--- a/scripts/ground-truth/judah-2026-05-02.xlsx
+++ b/scripts/ground-truth/judah-2026-05-02.xlsx
@@ -1,41 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D18AAD0-875D-4170-B15A-8238734321EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="9430" yWindow="-10910" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9430" yWindow="-10910" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="Metadata" sheetId="2" r:id="rId2"/>
-    <sheet name="Goals" sheetId="3" r:id="rId3"/>
-    <sheet name="Saves" sheetId="4" r:id="rId4"/>
-    <sheet name="Crosses" sheetId="6" r:id="rId5"/>
-    <sheet name="Distribution" sheetId="5" r:id="rId6"/>
-    <sheet name="Sweeper" sheetId="7" r:id="rId7"/>
-    <sheet name="1v1s" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Metadata" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Goals" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Saves" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="Crosses" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="Distribution" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Sweeper" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="1v1s" state="visible" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="232">
   <si>
     <t>STIX Match Ground-Truth Tagger</t>
   </si>
@@ -112,6 +98,9 @@
     <t>Match name</t>
   </si>
   <si>
+    <t>judah-vs-kcity2016gold-2026-04-25</t>
+  </si>
+  <si>
     <t>Short slug for the match (used as filename and id)</t>
   </si>
   <si>
@@ -124,6 +113,9 @@
     <t>Opponent</t>
   </si>
   <si>
+    <t>KCITY FC 2016 Gold</t>
+  </si>
+  <si>
     <t>Opposition team name</t>
   </si>
   <si>
@@ -142,12 +134,18 @@
     <t>My team color</t>
   </si>
   <si>
+    <t>Grey</t>
+  </si>
+  <si>
     <t>Outfield jersey colour, lowercase</t>
   </si>
   <si>
     <t>Opponent color</t>
   </si>
   <si>
+    <t>Black</t>
+  </si>
+  <si>
     <t>My GK color</t>
   </si>
   <si>
@@ -172,6 +170,9 @@
     <t>video_job_id</t>
   </si>
   <si>
+    <t>bc00c75c-ffe8-4584-85e2-29f9aa492fa9</t>
+  </si>
+  <si>
     <t>Fill in after upload — needed for eval</t>
   </si>
   <si>
@@ -211,6 +212,9 @@
     <t>Open play</t>
   </si>
   <si>
+    <t>Driven</t>
+  </si>
+  <si>
     <t>6-Yard Box</t>
   </si>
   <si>
@@ -220,6 +224,42 @@
     <t>Centre</t>
   </si>
   <si>
+    <t>Right wing runs the ball to the end line, passes it back into the middle for a goal inside the 6-yard box</t>
+  </si>
+  <si>
+    <t>GK is set and ready for the shot but doesn't look to see if there is a pass option. Can't recover. Tries a "hockey" kick save.</t>
+  </si>
+  <si>
+    <t>24:36</t>
+  </si>
+  <si>
+    <t>Right Channel</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
+  <si>
+    <t>GK Left</t>
+  </si>
+  <si>
+    <t>Right wing wins the ball in the offensive half off the defender, drives to the net and shot near post for a goal</t>
+  </si>
+  <si>
+    <t>GK is set, but leaning back as the shot is taken. Goes off the hands and goal scored near post.</t>
+  </si>
+  <si>
+    <t>52:05</t>
+  </si>
+  <si>
+    <t>GK Right</t>
+  </si>
+  <si>
+    <t>Long ball played in, defender misses it on the bounce, and striker finishes first touch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GK waited to see the defenders move but the missed ball lead to a quick goal. Not fully set and on their heels. Didn't attack the ball </t>
+  </si>
+  <si>
     <t>Shot origin</t>
   </si>
   <si>
@@ -238,25 +278,235 @@
     <t>Body zone (A/B/C)</t>
   </si>
   <si>
+    <t>Deflection</t>
+  </si>
+  <si>
+    <t>Unclear</t>
+  </si>
+  <si>
+    <t>Catch</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Held</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Pass goes out far right, player drives to the baseline, shoots and deflected off a grey player. Bounces and GK grabs it.</t>
+  </si>
+  <si>
+    <t>GK attacks the ball as soon as the deflection happens. Bit on their heels but got to the ball first.</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>Player cuts back outside the 6 year box, dribbles in to shot but defender gets in the way</t>
+  </si>
+  <si>
+    <t>GK picks up the ball after deflecting through his players legs. He's set and couldn't attack the ball 1v1 as the defender cuts between the striker and the GK</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Smother</t>
+  </si>
+  <si>
+    <t>Unsuccessful corner kick. Ball bounces off players and GK gathers it up</t>
+  </si>
+  <si>
+    <t>GK gets off his line to get the ball in the 6 yard box</t>
+  </si>
+  <si>
+    <t>Foot</t>
+  </si>
+  <si>
+    <t>Parry</t>
+  </si>
+  <si>
+    <t>Corner</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Ball played in from out right into the middle, top of the 6, player shoots wide left</t>
+  </si>
+  <si>
+    <t>GK was covering right post, takes a strong power steps and dives lowgets fingers on it and parry wide for a corner</t>
+  </si>
+  <si>
+    <t>Corner kick, deflection off the black player, GK picks up a non-threatening ball.</t>
+  </si>
+  <si>
+    <t>Central Box</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Black players wins a ball in the middle, beats a player and takes a shot</t>
+  </si>
+  <si>
+    <t>GK shuffles to get cover the angle, makes the save going the other direction and smothers the ball safely</t>
+  </si>
+  <si>
+    <t>Black wins the ball in the middle, player advances to the top of the 6-yard box and shots low and left. GK save</t>
+  </si>
+  <si>
+    <t>GK is set and makes a strong dive to the left and holds the ball. No rebound</t>
+  </si>
+  <si>
+    <t>27:25</t>
+  </si>
+  <si>
+    <t>Rebound (dangerous)</t>
+  </si>
+  <si>
+    <t>Penalty taken. Driven low and to the GK right.</t>
+  </si>
+  <si>
+    <t>GK set. Reacts to the ball and makes the safe. Rebound to danger but kicked out.</t>
+  </si>
+  <si>
+    <t>30:31</t>
+  </si>
+  <si>
     <t>Central Distance</t>
   </si>
   <si>
-    <t>Foot</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Parry</t>
-  </si>
-  <si>
-    <t>Corner</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>GK Right</t>
+    <t>Long low shot taken. Rolls into the GK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GK ready and easily collects a long low shot. </t>
+  </si>
+  <si>
+    <t>38:13</t>
+  </si>
+  <si>
+    <t>Missed pass from Def to Def creating a 1v1</t>
+  </si>
+  <si>
+    <t>GK was charging at the striker and makes the block that goes out for a corner</t>
+  </si>
+  <si>
+    <t>38:38</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>Shot taken not visible but GK makes the save</t>
+  </si>
+  <si>
+    <t>GK set for the shot and handles cleanly</t>
+  </si>
+  <si>
+    <t>39:19</t>
+  </si>
+  <si>
+    <t>Small deflection from the striker off of a kick-in. GK well placed to handle</t>
+  </si>
+  <si>
+    <t>GK ready and collects bobbling deflected ball.</t>
+  </si>
+  <si>
+    <t>41:08</t>
+  </si>
+  <si>
+    <t>After GK tips a cross wide, player plays easy ball into the GK hands</t>
+  </si>
+  <si>
+    <t>GK gets set after tipping a cross and collects an easy ball.</t>
+  </si>
+  <si>
+    <t>41:48</t>
+  </si>
+  <si>
+    <t>Player turns and takes shot on goal.</t>
+  </si>
+  <si>
+    <t>44:28</t>
+  </si>
+  <si>
+    <t>Ball comes in from out of frame on the ground. GK calls for it and collects cleanly</t>
+  </si>
+  <si>
+    <t>GK ready for the long pass, comes off his line to collect the ball cleanly.</t>
+  </si>
+  <si>
+    <t>52:36</t>
+  </si>
+  <si>
+    <t>Rebound (safe)</t>
+  </si>
+  <si>
+    <t>Defender gives the ball away, weak shot gets pushed wide by GK</t>
+  </si>
+  <si>
+    <t>GK follows play, gets set once given away, and take strong power step to parry ball wide of the goal</t>
+  </si>
+  <si>
+    <t>Side</t>
+  </si>
+  <si>
+    <t>Cross type</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>GK starting pos</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>6yd</t>
+  </si>
+  <si>
+    <t>On line</t>
+  </si>
+  <si>
+    <t>Ball swung in off of a kick-in. GK handles the ball cleanly.</t>
+  </si>
+  <si>
+    <t>34:14</t>
+  </si>
+  <si>
+    <t>37:14</t>
+  </si>
+  <si>
+    <t>Looped</t>
+  </si>
+  <si>
+    <t>Ball was heading out and player kicks it over their own head. Small deflection by grey and picked up easily by the GK.</t>
+  </si>
+  <si>
+    <t>40:47</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Awkward unintentional ball from the wing, GK calls for it and holds the ball.</t>
+  </si>
+  <si>
+    <t>41:04</t>
+  </si>
+  <si>
+    <t>Punch</t>
+  </si>
+  <si>
+    <t>Punched away</t>
+  </si>
+  <si>
+    <t>Not a full punch, but a touch to put the striker off balance.</t>
   </si>
   <si>
     <t>QUICK TOTALS — fill these IN PLACE OF logging every event if you do not want to tag row-by-row.</t>
@@ -319,40 +569,136 @@
     <t>First touch</t>
   </si>
   <si>
+    <t>After save</t>
+  </si>
+  <si>
+    <t>Throw</t>
+  </si>
+  <si>
+    <t>Defender</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t>Ball rolled to the right back who had time to play it up to their winger.</t>
+  </si>
+  <si>
+    <t>GK rolled the ball to his left back who was pressured quickly and kicked the ball off the striker for a goalkick.</t>
+  </si>
+  <si>
+    <t>Goal kick</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Short to defender</t>
+  </si>
+  <si>
+    <t>Short goal kick to the left back, under pressure passes it to the center mid standing just outside of the 6 yeard box and kicks it out for a corner</t>
+  </si>
+  <si>
+    <t>Defender plays long ball up to where the center mid should be but creates a turnover.</t>
+  </si>
+  <si>
     <t>Backpass</t>
   </si>
   <si>
-    <t>Pass</t>
+    <t>Defender has a great first touch, couldn't find a player, passes it in a channel to the center mid who is beat to the ball.</t>
+  </si>
+  <si>
+    <t>Right back plays ball in the middle to the center mid, who loses the ball and a counter attack shot is created.</t>
+  </si>
+  <si>
+    <t>GK Short Kick</t>
+  </si>
+  <si>
+    <t>Ballplayed to the left back who makes a successful pass to the winger, who isn't able to advance the ball</t>
+  </si>
+  <si>
+    <t>Right back loses the ball to the attacking striker because of a lack of passing options</t>
+  </si>
+  <si>
+    <t>Right back moves the ball comfortably to the central mid who is in a lane ready to receive</t>
+  </si>
+  <si>
+    <t>Right back receives ball, beats the striker to the right and makes a successful pass to the mid</t>
+  </si>
+  <si>
+    <t>25:51</t>
+  </si>
+  <si>
+    <t>Right back has few options, loses ball to the attacking striker. Shot hits a D hand for a penalty.</t>
+  </si>
+  <si>
+    <t>34:15</t>
+  </si>
+  <si>
+    <t>Drop-kick</t>
   </si>
   <si>
     <t>Switch wide</t>
   </si>
   <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Defender</t>
-  </si>
-  <si>
-    <t>Clean</t>
-  </si>
-  <si>
-    <t>Side</t>
-  </si>
-  <si>
-    <t>Cross type</t>
-  </si>
-  <si>
-    <t>Destination</t>
-  </si>
-  <si>
-    <t>GK starting pos</t>
-  </si>
-  <si>
-    <t>Punch</t>
-  </si>
-  <si>
-    <t>Punched away</t>
+    <t>Midfielder</t>
+  </si>
+  <si>
+    <t>Excellent drop-kick precision for location. Controlled by right mid but ball lost on the second touch.</t>
+  </si>
+  <si>
+    <t>35:49</t>
+  </si>
+  <si>
+    <t>37:16</t>
+  </si>
+  <si>
+    <t>38:40</t>
+  </si>
+  <si>
+    <t>Long to forward</t>
+  </si>
+  <si>
+    <t>39:25</t>
+  </si>
+  <si>
+    <t>Right back plays ball across the crease out of trouble while under pressure</t>
+  </si>
+  <si>
+    <t>40:50</t>
+  </si>
+  <si>
+    <t>Opponent (turnover)</t>
+  </si>
+  <si>
+    <t>Long drop kick goes into the other crease, just out of reach from the striker.</t>
+  </si>
+  <si>
+    <t>41:11</t>
+  </si>
+  <si>
+    <t>41:55</t>
+  </si>
+  <si>
+    <t>Couldn't see the result of the throw, but ball ends up in the offensive zone for the grey team.</t>
+  </si>
+  <si>
+    <t>43:23</t>
+  </si>
+  <si>
+    <t>44:31</t>
+  </si>
+  <si>
+    <t>44:50</t>
+  </si>
+  <si>
+    <t>45:56</t>
+  </si>
+  <si>
+    <t>47:05</t>
+  </si>
+  <si>
+    <t>50:57</t>
   </si>
   <si>
     <t>Action</t>
@@ -370,377 +716,20 @@
     <t>1v1 faced</t>
   </si>
   <si>
-    <t>judah-vs-kcity2016gold-2026-04-25</t>
-  </si>
-  <si>
-    <t>KCITY FC 2016 Gold</t>
-  </si>
-  <si>
-    <t>Grey</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>Right Channel</t>
-  </si>
-  <si>
-    <t>Unclear</t>
-  </si>
-  <si>
-    <t>Catch</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Mid</t>
-  </si>
-  <si>
-    <t>Pass goes out far right, player drives to the baseline, shoots and deflected off a grey player. Bounces and GK grabs it.</t>
-  </si>
-  <si>
-    <t>GK attacks the ball as soon as the deflection happens. Bit on their heels but got to the ball first.</t>
-  </si>
-  <si>
-    <t>After save</t>
-  </si>
-  <si>
-    <t>Throw</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
-    <t>Ball rolled to the right back who had time to play it up to their winger.</t>
-  </si>
-  <si>
-    <t>Deflection</t>
-  </si>
-  <si>
-    <t>Block</t>
-  </si>
-  <si>
-    <t>GK Left</t>
-  </si>
-  <si>
-    <t>Player cuts back outside the 6 year box, dribbles in to shot but defender gets in the way</t>
-  </si>
-  <si>
-    <t>GK picks up the ball after deflecting through his players legs. He's set and couldn't attack the ball 1v1 as the defender cuts between the striker and the GK</t>
-  </si>
-  <si>
-    <t>GK rolled the ball to his left back who was pressured quickly and kicked the ball off the striker for a goalkick.</t>
-  </si>
-  <si>
-    <t>Goal kick</t>
-  </si>
-  <si>
-    <t>Short goal kick to the left back, under pressure passes it to the center mid standing just outside of the 6 yeard box and kicks it out for a corner</t>
-  </si>
-  <si>
-    <t>Smother</t>
-  </si>
-  <si>
-    <t>Held</t>
-  </si>
-  <si>
-    <t>Unsuccessful corner kick. Ball bounces off players and GK gathers it up</t>
-  </si>
-  <si>
-    <t>GK gets off his line to get the ball in the 6 yard box</t>
-  </si>
-  <si>
-    <t>Defender plays long ball up to where the center mid should be but creates a turnover.</t>
-  </si>
-  <si>
-    <t>Defender has a great first touch, couldn't find a player, passes it in a channel to the center mid who is beat to the ball.</t>
-  </si>
-  <si>
-    <t>Ball played in from out right into the middle, top of the 6, player shoots wide left</t>
-  </si>
-  <si>
-    <t>GK was covering right post, takes a strong power steps and dives lowgets fingers on it and parry wide for a corner</t>
-  </si>
-  <si>
-    <t>Corner kick, deflection off the black player, GK picks up a non-threatening ball.</t>
-  </si>
-  <si>
-    <t>Driven</t>
-  </si>
-  <si>
-    <t>6yd</t>
-  </si>
-  <si>
-    <t>On line</t>
-  </si>
-  <si>
-    <t>Ball swung in off of a kick-in. GK handles the ball cleanly.</t>
-  </si>
-  <si>
-    <t>Right back plays ball in the middle to the center mid, who loses the ball and a counter attack shot is created.</t>
-  </si>
-  <si>
-    <t>Central Box</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Black players wins a ball in the middle, beats a player and takes a shot</t>
-  </si>
-  <si>
-    <t>GK shuffles to get cover the angle, makes the save going the other direction and smothers the ball safely</t>
-  </si>
-  <si>
-    <t>Ballplayed to the left back who makes a successful pass to the winger, who isn't able to advance the ball</t>
-  </si>
-  <si>
-    <t>Right back loses the ball to the attacking striker because of a lack of passing options</t>
-  </si>
-  <si>
-    <t>Black wins the ball in the middle, player advances to the top of the 6-yard box and shots low and left. GK save</t>
-  </si>
-  <si>
-    <t>GK is set and makes a strong dive to the left and holds the ball. No rebound</t>
-  </si>
-  <si>
-    <t>Right back moves the ball comfortably to the central mid who is in a lane ready to receive</t>
-  </si>
-  <si>
-    <t>Right wing runs the ball to the end line, passes it back into the middle for a goal inside the 6-yard box</t>
-  </si>
-  <si>
-    <t>GK is set and ready for the shot but doesn't look to see if there is a pass option. Can't recover. Tries a "hockey" kick save.</t>
-  </si>
-  <si>
-    <t>Right back receives ball, beats the striker to the right and makes a successful pass to the mid</t>
-  </si>
-  <si>
-    <t>Right wing wins the ball in the offensive half off the defender, drives to the net and shot near post for a goal</t>
-  </si>
-  <si>
-    <t>GK is set, but leaning back as the shot is taken. Goes off the hands and goal scored near post.</t>
-  </si>
-  <si>
-    <t>Right back has few options, loses ball to the attacking striker. Shot hits a D hand for a penalty.</t>
-  </si>
-  <si>
-    <t>Rebound (safe)</t>
-  </si>
-  <si>
-    <t>Rebound (dangerous)</t>
-  </si>
-  <si>
-    <t>Penalty taken. Driven low and to the GK right.</t>
-  </si>
-  <si>
-    <t>GK set. Reacts to the ball and makes the safe. Rebound to danger but kicked out.</t>
-  </si>
-  <si>
-    <t>27:25</t>
-  </si>
-  <si>
-    <t>30:31</t>
-  </si>
-  <si>
-    <t>Long low shot taken. Rolls into the GK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GK ready and easily collects a long low shot. </t>
-  </si>
-  <si>
-    <t>25:51</t>
-  </si>
-  <si>
-    <t>34:14</t>
-  </si>
-  <si>
-    <t>34:15</t>
-  </si>
-  <si>
-    <t>Drop-kick</t>
-  </si>
-  <si>
-    <t>Midfielder</t>
-  </si>
-  <si>
-    <t>Excellent drop-kick precision for location. Controlled by right mid but ball lost on the second touch.</t>
-  </si>
-  <si>
-    <t>35:49</t>
-  </si>
-  <si>
-    <t>GK Short Kick</t>
-  </si>
-  <si>
-    <t>Looped</t>
-  </si>
-  <si>
-    <t>Ball was heading out and player kicks it over their own head. Small deflection by grey and picked up easily by the GK.</t>
-  </si>
-  <si>
-    <t>37:14</t>
-  </si>
-  <si>
-    <t>37:16</t>
-  </si>
-  <si>
-    <t>38:13</t>
-  </si>
-  <si>
     <t>Saved</t>
-  </si>
-  <si>
-    <t>Missed pass from Def to Def creating a 1v1</t>
-  </si>
-  <si>
-    <t>GK was charging at the striker and makes the block that goes out for a corner</t>
-  </si>
-  <si>
-    <t>38:38</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>Shot taken not visible but GK makes the save</t>
-  </si>
-  <si>
-    <t>GK set for the shot and handles cleanly</t>
-  </si>
-  <si>
-    <t>38:40</t>
-  </si>
-  <si>
-    <t>39:19</t>
-  </si>
-  <si>
-    <t>Small deflection from the striker off of a kick-in. GK well placed to handle</t>
-  </si>
-  <si>
-    <t>GK ready and collects bobbling deflected ball.</t>
-  </si>
-  <si>
-    <t>39:25</t>
-  </si>
-  <si>
-    <t>Right back plays ball across the crease out of trouble while under pressure</t>
-  </si>
-  <si>
-    <t>Awkward unintentional ball from the wing, GK calls for it and holds the ball.</t>
-  </si>
-  <si>
-    <t>40:47</t>
-  </si>
-  <si>
-    <t>40:50</t>
-  </si>
-  <si>
-    <t>Opponent (turnover)</t>
-  </si>
-  <si>
-    <t>Long drop kick goes into the other crease, just out of reach from the striker.</t>
-  </si>
-  <si>
-    <t>41:04</t>
-  </si>
-  <si>
-    <t>Not a full punch, but a touch to put the striker off balance.</t>
-  </si>
-  <si>
-    <t>41:08</t>
-  </si>
-  <si>
-    <t>After GK tips a cross wide, player plays easy ball into the GK hands</t>
-  </si>
-  <si>
-    <t>GK gets set after tipping a cross and collects an easy ball.</t>
-  </si>
-  <si>
-    <t>41:11</t>
-  </si>
-  <si>
-    <t>Short to defender</t>
-  </si>
-  <si>
-    <t>Long to forward</t>
-  </si>
-  <si>
-    <t>41:48</t>
-  </si>
-  <si>
-    <t>Player turns and takes shot on goal.</t>
-  </si>
-  <si>
-    <t>41:55</t>
-  </si>
-  <si>
-    <t>Couldn't see the result of the throw, but ball ends up in the offensive zone for the grey team.</t>
-  </si>
-  <si>
-    <t>43:23</t>
-  </si>
-  <si>
-    <t>44:28</t>
-  </si>
-  <si>
-    <t>Ball comes in from out of frame on the ground. GK calls for it and collects cleanly</t>
-  </si>
-  <si>
-    <t>GK ready for the long pass, comes off his line to collect the ball cleanly.</t>
-  </si>
-  <si>
-    <t>44:31</t>
-  </si>
-  <si>
-    <t>44:50</t>
-  </si>
-  <si>
-    <t>45:56</t>
-  </si>
-  <si>
-    <t>47:05</t>
-  </si>
-  <si>
-    <t>24:36</t>
-  </si>
-  <si>
-    <t>52:05</t>
-  </si>
-  <si>
-    <t>Long ball played in, defender misses it on the bounce, and striker finishes first touch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GK waited to see the defenders move but the missed ball lead to a quick goal. Not fully set and on their heels. Didn't attack the ball </t>
-  </si>
-  <si>
-    <t>52:36</t>
-  </si>
-  <si>
-    <t>Defender gives the ball away, weak shot gets pushed wide by GK</t>
-  </si>
-  <si>
-    <t>GK follows play, gets set once given away, and take strong power step to parry ball wide of the goal</t>
-  </si>
-  <si>
-    <t>50:57</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -748,8 +737,8 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF333333"/>
       <sz val="11"/>
-      <color rgb="FF333333"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -759,14 +748,14 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
-      <color rgb="FF666666"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -815,10 +804,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1161,151 +1150,151 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF888888"/>
   </sheetPr>
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF666666"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>21</v>
       </c>
@@ -1316,149 +1305,149 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="5">
         <v>46144</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B11" s="6">
-        <v>2.3111111111111109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2.311111111110222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="B10" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B10">
       <formula1>"U6,U7,U8,U9,U10,U11,U12,U13,U14,U15,U16,U17,U18,Senior"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B5" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B5">
       <formula1>"Home,Away,Neutral"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B6" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B6">
       <formula1>"Match,Friendly,Training"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFEF4444"/>
   </sheetPr>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1470,173 +1459,194 @@
     <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>0.78263888888888888</v>
+        <v>0.7826388888897782</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="J2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>223</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="J3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>224</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="J4" t="s">
-        <v>226</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B201" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B201">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C201" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B201">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C201">
       <formula1>"Us,Opponent"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D201" xr:uid="{00000000-0002-0000-0200-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C201">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D201">
       <formula1>"Open play,Counter attack,Corner,Free kick,Penalty,Throw-in,Set piece other,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E201" xr:uid="{00000000-0002-0000-0200-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D201">
+      <formula1>"Open play,Counter attack,Corner,Free kick,Penalty,Throw-in,Set piece other,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E201">
       <formula1>"Header,Driven,Tap-in,Volley,Half-volley,Curled,Chip,One-v-one finish,Rebound,Deflection,Penalty,Free-kick,Own goal,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F201" xr:uid="{00000000-0002-0000-0200-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E201">
+      <formula1>"Header,Driven,Tap-in,Volley,Half-volley,Curled,Chip,One-v-one finish,Rebound,Deflection,Penalty,Free-kick,Own goal,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F201">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G201" xr:uid="{00000000-0002-0000-0200-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F201">
+      <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G201">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H201" xr:uid="{00000000-0002-0000-0200-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G201">
+      <formula1>"Top,Mid,Low,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H201">
+      <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H2:H201">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1651,1025 +1661,808 @@
     <col min="14" max="14" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>3.0555555555555555E-2</v>
+        <v>0.030555555556929903</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J2" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="K2" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L2" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="M2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>7.7777777777777779E-2</v>
+        <v>0.07777777777664596</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K3" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L3" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
-        <v>0.1111111111111111</v>
+        <v>0.11111111110949423</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L4" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
-        <v>0.35833333333333334</v>
+        <v>0.35833333333357587</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="I5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" t="s">
         <v>72</v>
       </c>
-      <c r="J5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" t="s">
-        <v>129</v>
-      </c>
       <c r="L5" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>0.50486111111111109</v>
+        <v>0.5048611111124046</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I6" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
-        <v>0.55972222222222223</v>
+        <v>0.5597222222204437</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="J7" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L7" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="M7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
-        <v>0.76875000000000004</v>
+        <v>0.7687499999992724</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" t="s">
         <v>72</v>
       </c>
-      <c r="J8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" t="s">
-        <v>129</v>
-      </c>
       <c r="L8" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>168</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="I9" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="J9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L9" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="M9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>169</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K10" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L10" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="M10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>184</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="I11" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K11" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L11" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="M11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>188</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>124</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="K12" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L12" t="s">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="M12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>193</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F13" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L13" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="M13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>205</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="K14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L14" t="s">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="M14" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>211</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" t="s">
+        <v>90</v>
+      </c>
+      <c r="J15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" t="s">
+        <v>135</v>
+      </c>
+      <c r="M15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="I15" t="s">
-        <v>118</v>
-      </c>
-      <c r="J15" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" t="s">
-        <v>212</v>
-      </c>
-      <c r="M15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>216</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K16" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L16" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="M16" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>227</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="I17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" t="s">
+        <v>65</v>
+      </c>
+      <c r="K17" t="s">
         <v>72</v>
       </c>
-      <c r="J17" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" t="s">
-        <v>129</v>
-      </c>
       <c r="L17" t="s">
-        <v>228</v>
+        <v>141</v>
       </c>
       <c r="M17" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" s="9"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="9"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="9"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="9"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="9"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" s="9"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" s="9"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" s="9"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A27" s="8"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B200" xr:uid="{00000000-0002-0000-0300-000000000000}">
+  <dataValidations count="20">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B200">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C200" xr:uid="{00000000-0002-0000-0300-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B200">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C200">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D200" xr:uid="{00000000-0002-0000-0300-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C200">
+      <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D200">
       <formula1>"Foot,Header,Deflection"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E200" xr:uid="{00000000-0002-0000-0300-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D200">
+      <formula1>"Foot,Header,Deflection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E200">
       <formula1>"Yes,No,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F200" xr:uid="{00000000-0002-0000-0300-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E200">
+      <formula1>"Yes,No,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F200">
       <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G200" xr:uid="{00000000-0002-0000-0300-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F200">
+      <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G200">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H200" xr:uid="{00000000-0002-0000-0300-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G200">
+      <formula1>"Yes,Partial,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H200">
       <formula1>"Held,Rebound (safe),Rebound (dangerous),Corner,Out of play,Goal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I200" xr:uid="{00000000-0002-0000-0300-00000E000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H200">
+      <formula1>"Held,Rebound (safe),Rebound (dangerous),Corner,Out of play,Goal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I10:I200">
       <formula1>"A,B,C,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J200" xr:uid="{00000000-0002-0000-0300-000010000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I200">
+      <formula1>"A,B,C,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J10:J200">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K200" xr:uid="{00000000-0002-0000-0300-000012000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J200">
+      <formula1>"Top,Mid,Low,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K10:K200">
+      <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K2:K200">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFF97316"/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
-        <v>0.55208333333333337</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H5" t="s">
-        <v>136</v>
-      </c>
-      <c r="I5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" t="s">
-        <v>145</v>
-      </c>
-      <c r="F6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H6" t="s">
-        <v>105</v>
-      </c>
-      <c r="I6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="9"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="9"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="10"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="10"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="10"/>
-    </row>
-  </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B201" xr:uid="{00000000-0002-0000-0500-000000000000}">
-      <formula1>"1,2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C201" xr:uid="{00000000-0002-0000-0500-000002000000}">
-      <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D201" xr:uid="{00000000-0002-0000-0500-000004000000}">
-      <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E201" xr:uid="{00000000-0002-0000-0500-000006000000}">
-      <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F201" xr:uid="{00000000-0002-0000-0500-000008000000}">
-      <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G201" xr:uid="{00000000-0002-0000-0500-00000A000000}">
-      <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H201" xr:uid="{00000000-0002-0000-0500-00000C000000}">
-      <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF3B82F6"/>
   </sheetPr>
   <dimension ref="A1:K46"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -2684,9 +2477,9 @@
     <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2694,9 +2487,9 @@
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -2704,451 +2497,451 @@
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>93</v>
+        <v>181</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
-        <v>3.3333333333333333E-2</v>
+        <v>0.03333333333284827</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="H17" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I17" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J17" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
-        <v>8.0555555555555561E-2</v>
+        <v>0.08055555555620231</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="H18" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
-        <v>9.4444444444444442E-2</v>
+        <v>0.0944444444430701</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G19" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H19" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I19" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
-        <v>0.11597222222222223</v>
+        <v>0.11597222222189885</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="H20" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J20" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
-        <v>0.14305555555555555</v>
+        <v>0.1430555555562023</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H21" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I21" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
-        <v>0.24027777777777778</v>
+        <v>0.24027777777882875</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F22" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G22" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H22" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I22" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J22" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K22" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
-        <v>0.38611111111111113</v>
+        <v>0.3861111111109494</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F23" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H23" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I23" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J23" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
-        <v>0.5541666666666667</v>
+        <v>0.5541666666649689</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E24" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="H24" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I24" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J24" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K24" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
-        <v>0.56388888888888888</v>
+        <v>0.5638888888897782</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F25" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H25" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I25" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
-        <v>0.69861111111111107</v>
+        <v>0.6986111111109494</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D26" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G26" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H26" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I26" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J26" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K26" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>0.71875</v>
       </c>
@@ -3156,624 +2949,624 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D27" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F27" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H27" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J27" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
-        <v>0.77222222222222225</v>
+        <v>0.7722222222218988</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H28" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I28" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J28" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
-        <v>0.88680555555555551</v>
+        <v>0.8868055555540195</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D29" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H29" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I29" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J29" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
-        <v>0.95138888888888884</v>
+        <v>0.9513888888905058</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G30" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H30" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I30" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J30" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K30" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="s">
-        <v>172</v>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H31" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I31" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J31" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K31" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="s">
-        <v>169</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>117</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D32" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H32" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I32" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J32" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="s">
-        <v>174</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>203</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D33" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F33" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="H33" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I33" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="J33" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K33" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
-        <v>178</v>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>208</v>
       </c>
       <c r="B34">
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D34" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G34" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" t="s">
+        <v>156</v>
+      </c>
+      <c r="I34" t="s">
+        <v>184</v>
+      </c>
+      <c r="J34" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="H34" t="s">
-        <v>97</v>
-      </c>
-      <c r="I34" t="s">
-        <v>98</v>
-      </c>
-      <c r="J34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A35" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I35" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J35" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A36" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D36" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="F36" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G36" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A37" s="9" t="s">
-        <v>196</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I37" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J37" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="K37" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A38" s="9" t="s">
-        <v>200</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>214</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F38" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G38" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H38" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I38" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="K38" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A39" s="9" t="s">
-        <v>208</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>217</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F39" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G39" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H39" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I39" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J39" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A40" s="9" t="s">
-        <v>213</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>218</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="K40" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A41" s="9" t="s">
-        <v>215</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E41" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F41" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G41" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H41" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I41" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J41" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
-        <v>219</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D42" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="E42" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F42" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G42" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H42" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="I42" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J42" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
-        <v>220</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F43" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G43" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H43" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I43" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J43" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A44" s="9" t="s">
-        <v>221</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F44" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G44" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H44" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I44" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J44" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A45" s="9" t="s">
-        <v>222</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>224</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F45" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="H45" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I45" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="J45" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A46" s="9" t="s">
-        <v>230</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>225</v>
       </c>
       <c r="B46">
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="D46" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E46" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F46" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G46" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="H46" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="I46" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="J46" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -3781,44 +3574,336 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" sqref="B17:B216" xr:uid="{00000000-0002-0000-0400-000000000000}">
+  <dataValidations count="16">
+    <dataValidation type="list" allowBlank="1" sqref="B100:B216">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C17:C216" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B17:B216">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C100:C216">
       <formula1>"Goal kick,After save,Backpass,Loose ball in box,Throw-in to GK,Free kick to GK"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D17:D216" xr:uid="{00000000-0002-0000-0400-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C17:C216">
+      <formula1>"Goal kick,After save,Backpass,Loose ball in box,Throw-in to GK,Free kick to GK"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D100:D216">
       <formula1>"GK Short Kick,GK Long Kick,Throw,Pass,Drop-kick"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E17:F216" xr:uid="{00000000-0002-0000-0400-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D17:D216">
+      <formula1>"GK Short Kick,GK Long Kick,Throw,Pass,Drop-kick"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E100:F216">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G17:G216" xr:uid="{00000000-0002-0000-0400-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E17:F216">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G100:G216">
       <formula1>"Short to defender,Sideways across back,Long to forward,Switch wide,Backwards under pressure,Clearance under pressure,Drilled into channel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H17:H216" xr:uid="{00000000-0002-0000-0400-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G17:G216">
+      <formula1>"Short to defender,Sideways across back,Long to forward,Switch wide,Backwards under pressure,Clearance under pressure,Drilled into channel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H100:H216">
       <formula1>"Left,Centre,Right,Backwards"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I17:I216" xr:uid="{00000000-0002-0000-0400-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H17:H216">
+      <formula1>"Left,Centre,Right,Backwards"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I100:I216">
       <formula1>"Defender,Midfielder,Forward,Out of play,Opponent (turnover)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J17:J216" xr:uid="{00000000-0002-0000-0400-00000E000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I17:I216">
+      <formula1>"Defender,Midfielder,Forward,Out of play,Opponent (turnover)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J100:J216">
+      <formula1>"Clean,Heavy,Two touches,Mishit"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J17:J216">
       <formula1>"Clean,Heavy,Two touches,Mishit"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFF97316"/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>0.5520833333321207</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+    </row>
+  </sheetData>
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B201">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="B2:B201">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C201">
+      <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C201">
+      <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D201">
+      <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D201">
+      <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E201">
+      <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E2:E201">
+      <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F201">
+      <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F2:F201">
+      <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G201">
+      <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G2:G201">
+      <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H201">
+      <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H2:H201">
+      <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFA78BFA"/>
   </sheetPr>
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -3830,65 +3915,83 @@
     <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>107</v>
+        <v>227</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B201" xr:uid="{00000000-0002-0000-0600-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B201">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C201" xr:uid="{00000000-0002-0000-0600-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B201">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C201">
       <formula1>"Clearance,Interception,Tackle,Header"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D201" xr:uid="{00000000-0002-0000-0600-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C201">
+      <formula1>"Clearance,Interception,Tackle,Header"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D201">
       <formula1>"In box,Edge of box,5–15 yards out,15+ yards out"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E201" xr:uid="{00000000-0002-0000-0600-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D201">
+      <formula1>"In box,Edge of box,5–15 yards out,15+ yards out"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E201">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F201" xr:uid="{00000000-0002-0000-0600-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E201">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F201">
       <formula1>"None,1 attacker,2+ attackers"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G201" xr:uid="{00000000-0002-0000-0600-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F201">
+      <formula1>"None,1 attacker,2+ attackers"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G201">
+      <formula1>"Possession retained,Cleared safely,Conceded turnover,Goal conceded"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G2:G201">
       <formula1>"Possession retained,Cleared safely,Conceded turnover,Goal conceded"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD4A853"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -3897,92 +4000,101 @@
     <col min="5" max="5" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
-        <v>184</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="9"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="9"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="9"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="9"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="9"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B201" xr:uid="{00000000-0002-0000-0700-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B201">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C201" xr:uid="{00000000-0002-0000-0700-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B201">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C201">
       <formula1>"1v1 faced,Recovery save,Error leading to goal,Big moment (other)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D201" xr:uid="{00000000-0002-0000-0700-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C201">
+      <formula1>"1v1 faced,Recovery save,Error leading to goal,Big moment (other)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D201">
+      <formula1>"Won,Conceded,Saved,Cleared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D201">
       <formula1>"Won,Conceded,Saved,Cleared"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>